--- a/AAII_Financials/Yearly/CCC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CCC_YR_FIN.xlsx
@@ -741,13 +741,13 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>262700</v>
+        <v>262200</v>
       </c>
       <c r="E9" s="3">
-        <v>222000</v>
+        <v>221400</v>
       </c>
       <c r="F9" s="3">
-        <v>203300</v>
+        <v>194200</v>
       </c>
       <c r="G9" s="3">
         <v>187000</v>
@@ -771,13 +771,13 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>794300</v>
+        <v>794800</v>
       </c>
       <c r="E10" s="3">
-        <v>722800</v>
+        <v>723400</v>
       </c>
       <c r="F10" s="3">
-        <v>663100</v>
+        <v>672200</v>
       </c>
       <c r="G10" s="3">
         <v>595400</v>
